--- a/public/prices/2026-09-17-zilma-price.xlsx
+++ b/public/prices/2026-09-17-zilma-price.xlsx
@@ -3050,7 +3050,7 @@
     <row r="120">
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ ABe-10 8200/0-ABe-10</t>
+          <t>Материя 80мл ABe-10 8200/0-ABe-10</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
@@ -3941,7 +3941,7 @@
     <row r="167">
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Шампунь "Jojoba" жожоба, для сухих волос, 1000мл 1576</t>
+          <t>Шампунь "Jojoba" жожоба, для сухих волос 1000мл 1576</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
@@ -6829,7 +6829,7 @@
     <row r="321">
       <c r="B321" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер д/окрашенных волос 1000мл 4765/10559</t>
+          <t>Кондиционер для окрашенных волос 1000мл 4765/10559</t>
         </is>
       </c>
       <c r="C321" s="36" t="n">
@@ -6841,9 +6841,7 @@
         </is>
       </c>
       <c r="E321" s="34" t="n"/>
-      <c r="F321" s="35" t="n">
-        <v>9</v>
-      </c>
+      <c r="F321" s="39" t="n"/>
     </row>
     <row r="322">
       <c r="B322" s="31" t="inlineStr">
